--- a/outputs/abatement_cost_curve_DACCS.xlsx
+++ b/outputs/abatement_cost_curve_DACCS.xlsx
@@ -413,13 +413,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>431.4796046076969</v>
+        <v>432.511661453333</v>
       </c>
       <c r="C3">
-        <v>288.9128446388541</v>
+        <v>289.1457860677647</v>
       </c>
       <c r="D3">
-        <v>1248.8760886334</v>
+        <v>1249.519407115362</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -427,13 +427,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>422.9470407423507</v>
+        <v>425.0111544336228</v>
       </c>
       <c r="C4">
-        <v>282.5212634733276</v>
+        <v>282.9871463311488</v>
       </c>
       <c r="D4">
-        <v>1215.437726736454</v>
+        <v>1216.724363700378</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -441,13 +441,13 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>414.4144768770045</v>
+        <v>417.5106474139127</v>
       </c>
       <c r="C5">
-        <v>276.1296823078011</v>
+        <v>276.828506594533</v>
       </c>
       <c r="D5">
-        <v>1181.999364839508</v>
+        <v>1183.929320285395</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -455,13 +455,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>405.8819130116582</v>
+        <v>410.0101403942026</v>
       </c>
       <c r="C6">
-        <v>269.7381011422747</v>
+        <v>270.6698668579171</v>
       </c>
       <c r="D6">
-        <v>1148.561002942562</v>
+        <v>1151.134276870411</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -469,13 +469,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>397.349349146312</v>
+        <v>402.5096333744925</v>
       </c>
       <c r="C7">
-        <v>263.3465199767482</v>
+        <v>264.5112271213013</v>
       </c>
       <c r="D7">
-        <v>1115.122641045616</v>
+        <v>1118.339233455427</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -483,13 +483,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>388.8167852809658</v>
+        <v>395.0091263547823</v>
       </c>
       <c r="C8">
-        <v>256.9549388112217</v>
+        <v>258.3525873846854</v>
       </c>
       <c r="D8">
-        <v>1081.68427914867</v>
+        <v>1085.544190040443</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -497,13 +497,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>380.2842214156196</v>
+        <v>387.5086193350722</v>
       </c>
       <c r="C9">
-        <v>250.5633576456952</v>
+        <v>252.1939476480695</v>
       </c>
       <c r="D9">
-        <v>1048.245917251724</v>
+        <v>1052.749146625459</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -511,13 +511,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>371.7516575502734</v>
+        <v>380.0081123153621</v>
       </c>
       <c r="C10">
-        <v>244.1717764801687</v>
+        <v>246.0353079114537</v>
       </c>
       <c r="D10">
-        <v>1014.807555354778</v>
+        <v>1019.954103210476</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -525,13 +525,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>363.2190936849271</v>
+        <v>372.507605295652</v>
       </c>
       <c r="C11">
-        <v>237.7801953146422</v>
+        <v>239.8766681748378</v>
       </c>
       <c r="D11">
-        <v>981.3691934578321</v>
+        <v>987.1590597954918</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -539,13 +539,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>354.6865298195809</v>
+        <v>365.0070982759418</v>
       </c>
       <c r="C12">
-        <v>231.3886141491158</v>
+        <v>233.7180284382219</v>
       </c>
       <c r="D12">
-        <v>947.9308315608862</v>
+        <v>954.364016380508</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -553,13 +553,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>346.1539659542347</v>
+        <v>357.5065912562317</v>
       </c>
       <c r="C13">
-        <v>224.9970329835893</v>
+        <v>227.5593887016061</v>
       </c>
       <c r="D13">
-        <v>914.4924696639401</v>
+        <v>921.5689729655242</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -567,13 +567,13 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>337.6214020888885</v>
+        <v>350.0060842365216</v>
       </c>
       <c r="C14">
-        <v>218.6054518180628</v>
+        <v>221.4007489649902</v>
       </c>
       <c r="D14">
-        <v>881.0541077669942</v>
+        <v>888.7739295505404</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -581,13 +581,13 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>329.0888382235423</v>
+        <v>342.5055772168114</v>
       </c>
       <c r="C15">
-        <v>212.2138706525363</v>
+        <v>215.2421092283743</v>
       </c>
       <c r="D15">
-        <v>847.6157458700482</v>
+        <v>855.9788861355566</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -595,13 +595,13 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>320.5562743581961</v>
+        <v>335.0050701971013</v>
       </c>
       <c r="C16">
-        <v>205.8222894870099</v>
+        <v>209.0834694917585</v>
       </c>
       <c r="D16">
-        <v>814.1773839731022</v>
+        <v>823.1838427205728</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -609,13 +609,13 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>312.0237104928499</v>
+        <v>327.5045631773912</v>
       </c>
       <c r="C17">
-        <v>199.4307083214834</v>
+        <v>202.9248297551426</v>
       </c>
       <c r="D17">
-        <v>780.7390220761563</v>
+        <v>790.3887993055889</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -623,13 +623,13 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>303.4911466275037</v>
+        <v>320.004056157681</v>
       </c>
       <c r="C18">
-        <v>193.0391271559569</v>
+        <v>196.7661900185267</v>
       </c>
       <c r="D18">
-        <v>747.3006601792102</v>
+        <v>757.5937558906052</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -637,13 +637,13 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>294.9585827621574</v>
+        <v>312.5035491379709</v>
       </c>
       <c r="C19">
-        <v>186.6475459904304</v>
+        <v>190.6075502819109</v>
       </c>
       <c r="D19">
-        <v>713.8622982822643</v>
+        <v>724.7987124756214</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -651,13 +651,13 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>286.4260188968112</v>
+        <v>305.0030421182607</v>
       </c>
       <c r="C20">
-        <v>180.2559648249039</v>
+        <v>184.448910545295</v>
       </c>
       <c r="D20">
-        <v>680.4239363853183</v>
+        <v>692.0036690606375</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -665,13 +665,13 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>277.893455031465</v>
+        <v>297.5025350985507</v>
       </c>
       <c r="C21">
-        <v>173.8643836593775</v>
+        <v>178.2902708086792</v>
       </c>
       <c r="D21">
-        <v>646.9855744883723</v>
+        <v>659.2086256456538</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -679,13 +679,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>269.3608911661188</v>
+        <v>290.0020280788405</v>
       </c>
       <c r="C22">
-        <v>167.472802493851</v>
+        <v>172.1316310720633</v>
       </c>
       <c r="D22">
-        <v>613.5472125914263</v>
+        <v>626.4135822306699</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -693,13 +693,13 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>260.8283273007726</v>
+        <v>282.5015210591304</v>
       </c>
       <c r="C23">
-        <v>161.0812213283245</v>
+        <v>165.9729913354474</v>
       </c>
       <c r="D23">
-        <v>580.1088506944803</v>
+        <v>593.6185388156862</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -707,13 +707,13 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>252.2957634354263</v>
+        <v>275.0010140394203</v>
       </c>
       <c r="C24">
-        <v>154.689640162798</v>
+        <v>159.8143515988316</v>
       </c>
       <c r="D24">
-        <v>546.6704887975343</v>
+        <v>560.8234954007023</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -721,13 +721,13 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>243.7631995700801</v>
+        <v>267.5005070197101</v>
       </c>
       <c r="C25">
-        <v>148.2980589972715</v>
+        <v>153.6557118622157</v>
       </c>
       <c r="D25">
-        <v>513.2321269005884</v>
+        <v>528.0284519857186</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -735,13 +735,13 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>235.2306357047339</v>
+        <v>260</v>
       </c>
       <c r="C26">
-        <v>141.9064778317451</v>
+        <v>147.4970721255999</v>
       </c>
       <c r="D26">
-        <v>479.7937650036424</v>
+        <v>495.2334085707348</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/abatement_cost_curve_DACCS.xlsx
+++ b/outputs/abatement_cost_curve_DACCS.xlsx
@@ -416,10 +416,10 @@
         <v>432.511661453333</v>
       </c>
       <c r="C3">
-        <v>289.1457860677647</v>
+        <v>288.493550066815</v>
       </c>
       <c r="D3">
-        <v>1249.519407115362</v>
+        <v>1248.898613675903</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -430,10 +430,10 @@
         <v>425.0111544336228</v>
       </c>
       <c r="C4">
-        <v>282.9871463311488</v>
+        <v>281.6826743292494</v>
       </c>
       <c r="D4">
-        <v>1216.724363700378</v>
+        <v>1215.48277682146</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -444,10 +444,10 @@
         <v>417.5106474139127</v>
       </c>
       <c r="C5">
-        <v>276.828506594533</v>
+        <v>274.8717985916838</v>
       </c>
       <c r="D5">
-        <v>1183.929320285395</v>
+        <v>1182.066939967017</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -458,10 +458,10 @@
         <v>410.0101403942026</v>
       </c>
       <c r="C6">
-        <v>270.6698668579171</v>
+        <v>268.0609228541182</v>
       </c>
       <c r="D6">
-        <v>1151.134276870411</v>
+        <v>1148.651103112574</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -472,10 +472,10 @@
         <v>402.5096333744925</v>
       </c>
       <c r="C7">
-        <v>264.5112271213013</v>
+        <v>261.2500471165527</v>
       </c>
       <c r="D7">
-        <v>1118.339233455427</v>
+        <v>1115.235266258131</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -486,10 +486,10 @@
         <v>395.0091263547823</v>
       </c>
       <c r="C8">
-        <v>258.3525873846854</v>
+        <v>254.439171378987</v>
       </c>
       <c r="D8">
-        <v>1085.544190040443</v>
+        <v>1081.819429403688</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -500,10 +500,10 @@
         <v>387.5086193350722</v>
       </c>
       <c r="C9">
-        <v>252.1939476480695</v>
+        <v>247.6282956414215</v>
       </c>
       <c r="D9">
-        <v>1052.749146625459</v>
+        <v>1048.403592549245</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -514,10 +514,10 @@
         <v>380.0081123153621</v>
       </c>
       <c r="C10">
-        <v>246.0353079114537</v>
+        <v>240.8174199038559</v>
       </c>
       <c r="D10">
-        <v>1019.954103210476</v>
+        <v>1014.987755694802</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -528,10 +528,10 @@
         <v>372.507605295652</v>
       </c>
       <c r="C11">
-        <v>239.8766681748378</v>
+        <v>234.0065441662903</v>
       </c>
       <c r="D11">
-        <v>987.1590597954918</v>
+        <v>981.5719188403594</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -542,10 +542,10 @@
         <v>365.0070982759418</v>
       </c>
       <c r="C12">
-        <v>233.7180284382219</v>
+        <v>227.1956684287247</v>
       </c>
       <c r="D12">
-        <v>954.364016380508</v>
+        <v>948.1560819859164</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -556,10 +556,10 @@
         <v>357.5065912562317</v>
       </c>
       <c r="C13">
-        <v>227.5593887016061</v>
+        <v>220.3847926911591</v>
       </c>
       <c r="D13">
-        <v>921.5689729655242</v>
+        <v>914.7402451314736</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -570,10 +570,10 @@
         <v>350.0060842365216</v>
       </c>
       <c r="C14">
-        <v>221.4007489649902</v>
+        <v>213.5739169535935</v>
       </c>
       <c r="D14">
-        <v>888.7739295505404</v>
+        <v>881.3244082770306</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -584,10 +584,10 @@
         <v>342.5055772168114</v>
       </c>
       <c r="C15">
-        <v>215.2421092283743</v>
+        <v>206.7630412160279</v>
       </c>
       <c r="D15">
-        <v>855.9788861355566</v>
+        <v>847.9085714225876</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -598,10 +598,10 @@
         <v>335.0050701971013</v>
       </c>
       <c r="C16">
-        <v>209.0834694917585</v>
+        <v>199.9521654784623</v>
       </c>
       <c r="D16">
-        <v>823.1838427205728</v>
+        <v>814.4927345681447</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -612,10 +612,10 @@
         <v>327.5045631773912</v>
       </c>
       <c r="C17">
-        <v>202.9248297551426</v>
+        <v>193.1412897408968</v>
       </c>
       <c r="D17">
-        <v>790.3887993055889</v>
+        <v>781.0768977137018</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -626,10 +626,10 @@
         <v>320.004056157681</v>
       </c>
       <c r="C18">
-        <v>196.7661900185267</v>
+        <v>186.3304140033312</v>
       </c>
       <c r="D18">
-        <v>757.5937558906052</v>
+        <v>747.6610608592588</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -640,10 +640,10 @@
         <v>312.5035491379709</v>
       </c>
       <c r="C19">
-        <v>190.6075502819109</v>
+        <v>179.5195382657656</v>
       </c>
       <c r="D19">
-        <v>724.7987124756214</v>
+        <v>714.2452240048158</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -654,10 +654,10 @@
         <v>305.0030421182607</v>
       </c>
       <c r="C20">
-        <v>184.448910545295</v>
+        <v>172.7086625282</v>
       </c>
       <c r="D20">
-        <v>692.0036690606375</v>
+        <v>680.8293871503729</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -668,10 +668,10 @@
         <v>297.5025350985507</v>
       </c>
       <c r="C21">
-        <v>178.2902708086792</v>
+        <v>165.8977867906344</v>
       </c>
       <c r="D21">
-        <v>659.2086256456538</v>
+        <v>647.4135502959299</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -682,10 +682,10 @@
         <v>290.0020280788405</v>
       </c>
       <c r="C22">
-        <v>172.1316310720633</v>
+        <v>159.0869110530688</v>
       </c>
       <c r="D22">
-        <v>626.4135822306699</v>
+        <v>613.997713441487</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -696,10 +696,10 @@
         <v>282.5015210591304</v>
       </c>
       <c r="C23">
-        <v>165.9729913354474</v>
+        <v>152.2760353155032</v>
       </c>
       <c r="D23">
-        <v>593.6185388156862</v>
+        <v>580.581876587044</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -710,10 +710,10 @@
         <v>275.0010140394203</v>
       </c>
       <c r="C24">
-        <v>159.8143515988316</v>
+        <v>145.4651595779376</v>
       </c>
       <c r="D24">
-        <v>560.8234954007023</v>
+        <v>547.1660397326011</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -724,10 +724,10 @@
         <v>267.5005070197101</v>
       </c>
       <c r="C25">
-        <v>153.6557118622157</v>
+        <v>138.654283840372</v>
       </c>
       <c r="D25">
-        <v>528.0284519857186</v>
+        <v>513.7502028781581</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -738,10 +738,10 @@
         <v>260</v>
       </c>
       <c r="C26">
-        <v>147.4970721255999</v>
+        <v>131.8434081028064</v>
       </c>
       <c r="D26">
-        <v>495.2334085707348</v>
+        <v>480.3343660237152</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/abatement_cost_curve_DACCS.xlsx
+++ b/outputs/abatement_cost_curve_DACCS.xlsx
@@ -416,10 +416,10 @@
         <v>432.511661453333</v>
       </c>
       <c r="C3">
-        <v>288.493550066815</v>
+        <v>289.1457860677647</v>
       </c>
       <c r="D3">
-        <v>1248.898613675903</v>
+        <v>1249.519407115362</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -430,10 +430,10 @@
         <v>425.0111544336228</v>
       </c>
       <c r="C4">
-        <v>281.6826743292494</v>
+        <v>282.9871463311488</v>
       </c>
       <c r="D4">
-        <v>1215.48277682146</v>
+        <v>1216.724363700378</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -444,10 +444,10 @@
         <v>417.5106474139127</v>
       </c>
       <c r="C5">
-        <v>274.8717985916838</v>
+        <v>276.828506594533</v>
       </c>
       <c r="D5">
-        <v>1182.066939967017</v>
+        <v>1183.929320285395</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -458,10 +458,10 @@
         <v>410.0101403942026</v>
       </c>
       <c r="C6">
-        <v>268.0609228541182</v>
+        <v>270.6698668579171</v>
       </c>
       <c r="D6">
-        <v>1148.651103112574</v>
+        <v>1151.134276870411</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -472,10 +472,10 @@
         <v>402.5096333744925</v>
       </c>
       <c r="C7">
-        <v>261.2500471165527</v>
+        <v>264.5112271213013</v>
       </c>
       <c r="D7">
-        <v>1115.235266258131</v>
+        <v>1118.339233455427</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -486,10 +486,10 @@
         <v>395.0091263547823</v>
       </c>
       <c r="C8">
-        <v>254.439171378987</v>
+        <v>258.3525873846854</v>
       </c>
       <c r="D8">
-        <v>1081.819429403688</v>
+        <v>1085.544190040443</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -500,10 +500,10 @@
         <v>387.5086193350722</v>
       </c>
       <c r="C9">
-        <v>247.6282956414215</v>
+        <v>252.1939476480695</v>
       </c>
       <c r="D9">
-        <v>1048.403592549245</v>
+        <v>1052.749146625459</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -514,10 +514,10 @@
         <v>380.0081123153621</v>
       </c>
       <c r="C10">
-        <v>240.8174199038559</v>
+        <v>246.0353079114537</v>
       </c>
       <c r="D10">
-        <v>1014.987755694802</v>
+        <v>1019.954103210476</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -528,10 +528,10 @@
         <v>372.507605295652</v>
       </c>
       <c r="C11">
-        <v>234.0065441662903</v>
+        <v>239.8766681748378</v>
       </c>
       <c r="D11">
-        <v>981.5719188403594</v>
+        <v>987.1590597954918</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -542,10 +542,10 @@
         <v>365.0070982759418</v>
       </c>
       <c r="C12">
-        <v>227.1956684287247</v>
+        <v>233.7180284382219</v>
       </c>
       <c r="D12">
-        <v>948.1560819859164</v>
+        <v>954.364016380508</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -556,10 +556,10 @@
         <v>357.5065912562317</v>
       </c>
       <c r="C13">
-        <v>220.3847926911591</v>
+        <v>227.5593887016061</v>
       </c>
       <c r="D13">
-        <v>914.7402451314736</v>
+        <v>921.5689729655242</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -570,10 +570,10 @@
         <v>350.0060842365216</v>
       </c>
       <c r="C14">
-        <v>213.5739169535935</v>
+        <v>221.4007489649902</v>
       </c>
       <c r="D14">
-        <v>881.3244082770306</v>
+        <v>888.7739295505404</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -584,10 +584,10 @@
         <v>342.5055772168114</v>
       </c>
       <c r="C15">
-        <v>206.7630412160279</v>
+        <v>215.2421092283743</v>
       </c>
       <c r="D15">
-        <v>847.9085714225876</v>
+        <v>855.9788861355566</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -598,10 +598,10 @@
         <v>335.0050701971013</v>
       </c>
       <c r="C16">
-        <v>199.9521654784623</v>
+        <v>209.0834694917585</v>
       </c>
       <c r="D16">
-        <v>814.4927345681447</v>
+        <v>823.1838427205728</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -612,10 +612,10 @@
         <v>327.5045631773912</v>
       </c>
       <c r="C17">
-        <v>193.1412897408968</v>
+        <v>202.9248297551426</v>
       </c>
       <c r="D17">
-        <v>781.0768977137018</v>
+        <v>790.3887993055889</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -626,10 +626,10 @@
         <v>320.004056157681</v>
       </c>
       <c r="C18">
-        <v>186.3304140033312</v>
+        <v>196.7661900185267</v>
       </c>
       <c r="D18">
-        <v>747.6610608592588</v>
+        <v>757.5937558906052</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -640,10 +640,10 @@
         <v>312.5035491379709</v>
       </c>
       <c r="C19">
-        <v>179.5195382657656</v>
+        <v>190.6075502819109</v>
       </c>
       <c r="D19">
-        <v>714.2452240048158</v>
+        <v>724.7987124756214</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -654,10 +654,10 @@
         <v>305.0030421182607</v>
       </c>
       <c r="C20">
-        <v>172.7086625282</v>
+        <v>184.448910545295</v>
       </c>
       <c r="D20">
-        <v>680.8293871503729</v>
+        <v>692.0036690606375</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -668,10 +668,10 @@
         <v>297.5025350985507</v>
       </c>
       <c r="C21">
-        <v>165.8977867906344</v>
+        <v>178.2902708086792</v>
       </c>
       <c r="D21">
-        <v>647.4135502959299</v>
+        <v>659.2086256456538</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -682,10 +682,10 @@
         <v>290.0020280788405</v>
       </c>
       <c r="C22">
-        <v>159.0869110530688</v>
+        <v>172.1316310720633</v>
       </c>
       <c r="D22">
-        <v>613.997713441487</v>
+        <v>626.4135822306699</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -696,10 +696,10 @@
         <v>282.5015210591304</v>
       </c>
       <c r="C23">
-        <v>152.2760353155032</v>
+        <v>165.9729913354474</v>
       </c>
       <c r="D23">
-        <v>580.581876587044</v>
+        <v>593.6185388156862</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -710,10 +710,10 @@
         <v>275.0010140394203</v>
       </c>
       <c r="C24">
-        <v>145.4651595779376</v>
+        <v>159.8143515988316</v>
       </c>
       <c r="D24">
-        <v>547.1660397326011</v>
+        <v>560.8234954007023</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -724,10 +724,10 @@
         <v>267.5005070197101</v>
       </c>
       <c r="C25">
-        <v>138.654283840372</v>
+        <v>153.6557118622157</v>
       </c>
       <c r="D25">
-        <v>513.7502028781581</v>
+        <v>528.0284519857186</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -738,10 +738,10 @@
         <v>260</v>
       </c>
       <c r="C26">
-        <v>131.8434081028064</v>
+        <v>147.4970721255999</v>
       </c>
       <c r="D26">
-        <v>480.3343660237152</v>
+        <v>495.2334085707348</v>
       </c>
     </row>
   </sheetData>

--- a/outputs/abatement_cost_curve_DACCS.xlsx
+++ b/outputs/abatement_cost_curve_DACCS.xlsx
@@ -399,13 +399,13 @@
         <v>0</v>
       </c>
       <c r="B2">
-        <v>440.0121684730431</v>
+        <v>590.9227946568607</v>
       </c>
       <c r="C2">
-        <v>295.3044258043806</v>
+        <v>339.9069710626542</v>
       </c>
       <c r="D2">
-        <v>1282.314450530346</v>
+        <v>1371.471974359897</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -413,13 +413,13 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>432.511661453333</v>
+        <v>579.2882120103336</v>
       </c>
       <c r="C3">
-        <v>289.1457860677647</v>
+        <v>332.3968256857534</v>
       </c>
       <c r="D3">
-        <v>1249.519407115362</v>
+        <v>1336.941892094901</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -427,13 +427,13 @@
         <v>2</v>
       </c>
       <c r="B4">
-        <v>425.0111544336228</v>
+        <v>567.6536293638065</v>
       </c>
       <c r="C4">
-        <v>282.9871463311488</v>
+        <v>324.8866803088524</v>
       </c>
       <c r="D4">
-        <v>1216.724363700378</v>
+        <v>1302.411809829905</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -441,13 +441,13 @@
         <v>3</v>
       </c>
       <c r="B5">
-        <v>417.5106474139127</v>
+        <v>556.0190467172794</v>
       </c>
       <c r="C5">
-        <v>276.828506594533</v>
+        <v>317.3765349319515</v>
       </c>
       <c r="D5">
-        <v>1183.929320285395</v>
+        <v>1267.88172756491</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -455,13 +455,13 @@
         <v>4</v>
       </c>
       <c r="B6">
-        <v>410.0101403942026</v>
+        <v>544.3844640707523</v>
       </c>
       <c r="C6">
-        <v>270.6698668579171</v>
+        <v>309.8663895550507</v>
       </c>
       <c r="D6">
-        <v>1151.134276870411</v>
+        <v>1233.351645299914</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -469,13 +469,13 @@
         <v>5</v>
       </c>
       <c r="B7">
-        <v>402.5096333744925</v>
+        <v>532.7498814242252</v>
       </c>
       <c r="C7">
-        <v>264.5112271213013</v>
+        <v>302.3562441781497</v>
       </c>
       <c r="D7">
-        <v>1118.339233455427</v>
+        <v>1198.821563034918</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -483,13 +483,13 @@
         <v>6</v>
       </c>
       <c r="B8">
-        <v>395.0091263547823</v>
+        <v>521.1152987776982</v>
       </c>
       <c r="C8">
-        <v>258.3525873846854</v>
+        <v>294.8460988012488</v>
       </c>
       <c r="D8">
-        <v>1085.544190040443</v>
+        <v>1164.291480769923</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -497,13 +497,13 @@
         <v>7</v>
       </c>
       <c r="B9">
-        <v>387.5086193350722</v>
+        <v>509.4807161311711</v>
       </c>
       <c r="C9">
-        <v>252.1939476480695</v>
+        <v>287.3359534243479</v>
       </c>
       <c r="D9">
-        <v>1052.749146625459</v>
+        <v>1129.761398504927</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -511,13 +511,13 @@
         <v>8</v>
       </c>
       <c r="B10">
-        <v>380.0081123153621</v>
+        <v>497.846133484644</v>
       </c>
       <c r="C10">
-        <v>246.0353079114537</v>
+        <v>279.825808047447</v>
       </c>
       <c r="D10">
-        <v>1019.954103210476</v>
+        <v>1095.231316239931</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -525,13 +525,13 @@
         <v>9</v>
       </c>
       <c r="B11">
-        <v>372.507605295652</v>
+        <v>486.2115508381169</v>
       </c>
       <c r="C11">
-        <v>239.8766681748378</v>
+        <v>272.3156626705461</v>
       </c>
       <c r="D11">
-        <v>987.1590597954918</v>
+        <v>1060.701233974935</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -539,13 +539,13 @@
         <v>10</v>
       </c>
       <c r="B12">
-        <v>365.0070982759418</v>
+        <v>474.5769681915898</v>
       </c>
       <c r="C12">
-        <v>233.7180284382219</v>
+        <v>264.8055172936452</v>
       </c>
       <c r="D12">
-        <v>954.364016380508</v>
+        <v>1026.17115170994</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -553,13 +553,13 @@
         <v>11</v>
       </c>
       <c r="B13">
-        <v>357.5065912562317</v>
+        <v>462.9423855450627</v>
       </c>
       <c r="C13">
-        <v>227.5593887016061</v>
+        <v>257.2953719167443</v>
       </c>
       <c r="D13">
-        <v>921.5689729655242</v>
+        <v>991.641069444944</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -567,13 +567,13 @@
         <v>12</v>
       </c>
       <c r="B14">
-        <v>350.0060842365216</v>
+        <v>451.3078028985357</v>
       </c>
       <c r="C14">
-        <v>221.4007489649902</v>
+        <v>249.7852265398434</v>
       </c>
       <c r="D14">
-        <v>888.7739295505404</v>
+        <v>957.1109871799483</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -581,13 +581,13 @@
         <v>13</v>
       </c>
       <c r="B15">
-        <v>342.5055772168114</v>
+        <v>439.6732202520085</v>
       </c>
       <c r="C15">
-        <v>215.2421092283743</v>
+        <v>242.2750811629425</v>
       </c>
       <c r="D15">
-        <v>855.9788861355566</v>
+        <v>922.5809049149527</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -595,13 +595,13 @@
         <v>14</v>
       </c>
       <c r="B16">
-        <v>335.0050701971013</v>
+        <v>428.0386376054815</v>
       </c>
       <c r="C16">
-        <v>209.0834694917585</v>
+        <v>234.7649357860416</v>
       </c>
       <c r="D16">
-        <v>823.1838427205728</v>
+        <v>888.0508226499569</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -609,13 +609,13 @@
         <v>15</v>
       </c>
       <c r="B17">
-        <v>327.5045631773912</v>
+        <v>416.4040549589544</v>
       </c>
       <c r="C17">
-        <v>202.9248297551426</v>
+        <v>227.2547904091407</v>
       </c>
       <c r="D17">
-        <v>790.3887993055889</v>
+        <v>853.5207403849613</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -623,13 +623,13 @@
         <v>16</v>
       </c>
       <c r="B18">
-        <v>320.004056157681</v>
+        <v>404.7694723124273</v>
       </c>
       <c r="C18">
-        <v>196.7661900185267</v>
+        <v>219.7446450322398</v>
       </c>
       <c r="D18">
-        <v>757.5937558906052</v>
+        <v>818.9906581199656</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -637,13 +637,13 @@
         <v>17</v>
       </c>
       <c r="B19">
-        <v>312.5035491379709</v>
+        <v>393.1348896659002</v>
       </c>
       <c r="C19">
-        <v>190.6075502819109</v>
+        <v>212.2344996553389</v>
       </c>
       <c r="D19">
-        <v>724.7987124756214</v>
+        <v>784.4605758549699</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -651,13 +651,13 @@
         <v>18</v>
       </c>
       <c r="B20">
-        <v>305.0030421182607</v>
+        <v>381.5003070193731</v>
       </c>
       <c r="C20">
-        <v>184.448910545295</v>
+        <v>204.724354278438</v>
       </c>
       <c r="D20">
-        <v>692.0036690606375</v>
+        <v>749.9304935899742</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -665,13 +665,13 @@
         <v>19</v>
       </c>
       <c r="B21">
-        <v>297.5025350985507</v>
+        <v>369.865724372846</v>
       </c>
       <c r="C21">
-        <v>178.2902708086792</v>
+        <v>197.2142089015371</v>
       </c>
       <c r="D21">
-        <v>659.2086256456538</v>
+        <v>715.4004113249786</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -679,13 +679,13 @@
         <v>20</v>
       </c>
       <c r="B22">
-        <v>290.0020280788405</v>
+        <v>358.2311417263189</v>
       </c>
       <c r="C22">
-        <v>172.1316310720633</v>
+        <v>189.7040635246362</v>
       </c>
       <c r="D22">
-        <v>626.4135822306699</v>
+        <v>680.8703290599829</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -693,13 +693,13 @@
         <v>21</v>
       </c>
       <c r="B23">
-        <v>282.5015210591304</v>
+        <v>346.5965590797919</v>
       </c>
       <c r="C23">
-        <v>165.9729913354474</v>
+        <v>182.1939181477353</v>
       </c>
       <c r="D23">
-        <v>593.6185388156862</v>
+        <v>646.3402467949871</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -707,13 +707,13 @@
         <v>22</v>
       </c>
       <c r="B24">
-        <v>275.0010140394203</v>
+        <v>334.9619764332648</v>
       </c>
       <c r="C24">
-        <v>159.8143515988316</v>
+        <v>174.6837727708344</v>
       </c>
       <c r="D24">
-        <v>560.8234954007023</v>
+        <v>611.8101645299914</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -721,13 +721,13 @@
         <v>23</v>
       </c>
       <c r="B25">
-        <v>267.5005070197101</v>
+        <v>323.3273937867377</v>
       </c>
       <c r="C25">
-        <v>153.6557118622157</v>
+        <v>167.1736273939335</v>
       </c>
       <c r="D25">
-        <v>528.0284519857186</v>
+        <v>577.2800822649957</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -735,13 +735,13 @@
         <v>24</v>
       </c>
       <c r="B26">
-        <v>260</v>
+        <v>311.6928111402106</v>
       </c>
       <c r="C26">
-        <v>147.4970721255999</v>
+        <v>159.6634820170326</v>
       </c>
       <c r="D26">
-        <v>495.2334085707348</v>
+        <v>542.75</v>
       </c>
     </row>
   </sheetData>
